--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105358232</v>
+        <v>105359035</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576933.5214173985</v>
+        <v>576890</v>
       </c>
       <c r="R2" t="n">
-        <v>7051166.415713439</v>
+        <v>7051115</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-12-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105358239</v>
+        <v>106186475</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576928.6168779061</v>
+        <v>576692</v>
       </c>
       <c r="R3" t="n">
-        <v>7051166.296880636</v>
+        <v>7050786</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +839,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105359091</v>
+        <v>109013264</v>
       </c>
       <c r="B4" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,13 +917,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576889.2721733196</v>
+        <v>577180</v>
       </c>
       <c r="R4" t="n">
-        <v>7051114.552547283</v>
+        <v>7050904</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +947,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105358131</v>
+        <v>109013661</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1025,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576977.648202814</v>
+        <v>577132</v>
       </c>
       <c r="R5" t="n">
-        <v>7051149.663770375</v>
+        <v>7050911</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105358298</v>
+        <v>109016013</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,43 +1108,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576912.1627719229</v>
+        <v>577001</v>
       </c>
       <c r="R6" t="n">
-        <v>7051108.869349363</v>
+        <v>7050818</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,27 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105358184</v>
+        <v>109018567</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,13 +1241,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576982.2828739712</v>
+        <v>576907</v>
       </c>
       <c r="R7" t="n">
-        <v>7051160.914546241</v>
+        <v>7051050</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1271,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,27 +1301,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105359395</v>
+        <v>109018888</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,43 +1324,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576941.7634994419</v>
+        <v>576942</v>
       </c>
       <c r="R8" t="n">
-        <v>7051047.209930972</v>
+        <v>7051159</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,22 +1379,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,37 +1421,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105359035</v>
+        <v>105358131</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576890.1639222496</v>
+        <v>576978</v>
       </c>
       <c r="R9" t="n">
-        <v>7051114.574141545</v>
+        <v>7051150</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,19 +1490,9 @@
           <t>2022-12-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,60 +1519,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106186581</v>
+        <v>105358184</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576703.2975478509</v>
+        <v>576982</v>
       </c>
       <c r="R10" t="n">
-        <v>7050779.446228665</v>
+        <v>7051161</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,22 +1585,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,19 +1617,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106185805</v>
+        <v>105358232</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1752,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577080.1143854944</v>
+        <v>576934</v>
       </c>
       <c r="R11" t="n">
-        <v>7051173.980849118</v>
+        <v>7051166</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,22 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,37 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106186475</v>
+        <v>106185805</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576692.4233577704</v>
+        <v>577081</v>
       </c>
       <c r="R12" t="n">
-        <v>7050786.312975749</v>
+        <v>7051174</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,7 +1786,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1796,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,37 +1823,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106186048</v>
+        <v>106185882</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576824.1313948807</v>
+        <v>577044</v>
       </c>
       <c r="R13" t="n">
-        <v>7051114.75796413</v>
+        <v>7051149</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2013,7 +1894,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +1904,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,19 +1931,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106185882</v>
+        <v>106185957</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2091,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577044.5934583726</v>
+        <v>577003</v>
       </c>
       <c r="R14" t="n">
-        <v>7051148.614248225</v>
+        <v>7051143</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2126,7 +2002,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2012,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,19 +2039,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106185957</v>
+        <v>109013961</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2204,13 +2075,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577002.7896770446</v>
+        <v>577121</v>
       </c>
       <c r="R15" t="n">
-        <v>7051143.14478629</v>
+        <v>7050876</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2234,22 +2105,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,27 +2135,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109018701</v>
+        <v>109018189</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576917.2831317006</v>
+        <v>576970</v>
       </c>
       <c r="R16" t="n">
-        <v>7051100.082521175</v>
+        <v>7050973</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2352,7 +2218,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2228,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,27 +2243,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109013589</v>
+        <v>105358298</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,13 +2296,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577135.5307122552</v>
+        <v>576912</v>
       </c>
       <c r="R17" t="n">
-        <v>7050912.895817635</v>
+        <v>7051109</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2465,22 +2326,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,15 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109016170</v>
+        <v>105359395</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,13 +2399,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577012.3409713482</v>
+        <v>576942</v>
       </c>
       <c r="R18" t="n">
-        <v>7050841.287124257</v>
+        <v>7051047</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2583,22 +2429,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,27 +2449,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109015538</v>
+        <v>106186581</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,11 +2489,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2671,13 +2506,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577066.0684749788</v>
+        <v>576704</v>
       </c>
       <c r="R19" t="n">
-        <v>7050704.90312257</v>
+        <v>7050779</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,22 +2536,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,27 +2566,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109014693</v>
+        <v>109012695</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2778,19 +2608,24 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kylbodarna, Ång</t>
+          <t>Kylklippen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577073.806548804</v>
+        <v>577205</v>
       </c>
       <c r="R20" t="n">
-        <v>7050808.914038404</v>
+        <v>7050972</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2819,7 +2654,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2664,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,27 +2679,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109013033</v>
+        <v>109012889</v>
       </c>
       <c r="B21" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,38 +2702,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577203.6435774869</v>
+        <v>577205</v>
       </c>
       <c r="R21" t="n">
-        <v>7050900.738330831</v>
+        <v>7050947</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2932,7 +2767,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2777,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,27 +2792,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109018004</v>
+        <v>109013388</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +2836,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3015,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576985.8066496834</v>
+        <v>577150</v>
       </c>
       <c r="R22" t="n">
-        <v>7050978.770681646</v>
+        <v>7050915</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3050,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,27 +2905,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109013867</v>
+        <v>109013589</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,13 +2958,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577132.1857796492</v>
+        <v>577136</v>
       </c>
       <c r="R23" t="n">
-        <v>7050866.920374339</v>
+        <v>7050913</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,7 +2993,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3003,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,27 +3018,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109013388</v>
+        <v>109013867</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,13 +3071,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577150.64813664</v>
+        <v>577133</v>
       </c>
       <c r="R24" t="n">
-        <v>7050915.045358492</v>
+        <v>7050866</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3286,7 +3106,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3296,7 +3116,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,27 +3131,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109014420</v>
+        <v>109014228</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3369,10 +3184,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577083.4032599393</v>
+        <v>577069</v>
       </c>
       <c r="R25" t="n">
-        <v>7050836.327577194</v>
+        <v>7050839</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
@@ -3404,7 +3219,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3414,7 +3229,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,15 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109019312</v>
+        <v>109014420</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,14 +3286,9 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3492,13 +3297,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577039.150751696</v>
+        <v>577083</v>
       </c>
       <c r="R26" t="n">
-        <v>7051115.512216642</v>
+        <v>7050836</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3527,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3537,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,15 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109013961</v>
+        <v>109014693</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3605,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577121.2676521187</v>
+        <v>577074</v>
       </c>
       <c r="R27" t="n">
-        <v>7050875.566740428</v>
+        <v>7050809</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
@@ -3640,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,12 +3480,7 @@
         <v>109015165</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3723,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577118.728500372</v>
+        <v>577118</v>
       </c>
       <c r="R28" t="n">
-        <v>7050759.653056217</v>
+        <v>7050760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3795,15 +3590,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109012695</v>
+        <v>109015538</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,22 +3622,22 @@
       <c r="K29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kylklippen, Ång</t>
+          <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577205.0434280515</v>
+        <v>577066</v>
       </c>
       <c r="R29" t="n">
-        <v>7050971.617799644</v>
+        <v>7050705</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3876,7 +3666,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3886,7 +3676,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,27 +3691,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109013661</v>
+        <v>109016063</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3929,38 +3714,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577131.5392182495</v>
+        <v>577006</v>
       </c>
       <c r="R30" t="n">
-        <v>7050911.907719217</v>
+        <v>7050828</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3989,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3999,7 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4014,27 +3804,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109014228</v>
+        <v>109016170</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577068.612453984</v>
+        <v>577013</v>
       </c>
       <c r="R31" t="n">
-        <v>7050839.087650675</v>
+        <v>7050842</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4107,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4117,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4132,27 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109016063</v>
+        <v>109016317</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4190,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577006.8572714403</v>
+        <v>576983</v>
       </c>
       <c r="R32" t="n">
-        <v>7050828.23227846</v>
+        <v>7050878</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4225,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4235,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4262,15 +4042,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109016013</v>
+        <v>109016758</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4278,35 +4053,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577000.852021958</v>
+        <v>577003</v>
       </c>
       <c r="R33" t="n">
-        <v>7050818.283832008</v>
+        <v>7050888</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -4338,7 +4118,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4348,7 +4128,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,15 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109017215</v>
+        <v>109017070</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4421,10 +4196,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577028.6141979052</v>
+        <v>577023</v>
       </c>
       <c r="R34" t="n">
-        <v>7050924.55873872</v>
+        <v>7050895</v>
       </c>
       <c r="S34" t="n">
         <v>2</v>
@@ -4456,7 +4231,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4241,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4493,15 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109017070</v>
+        <v>109017215</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4539,10 +4309,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577022.6277542652</v>
+        <v>577029</v>
       </c>
       <c r="R35" t="n">
-        <v>7050895.451409754</v>
+        <v>7050925</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4574,7 +4344,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4584,7 +4354,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4611,15 +4381,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109020099</v>
+        <v>109018004</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4657,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577018.0389856662</v>
+        <v>576985</v>
       </c>
       <c r="R36" t="n">
-        <v>7051029.454778589</v>
+        <v>7050979</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4692,7 +4457,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4702,7 +4467,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4717,12 +4482,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4732,12 +4497,7 @@
         <v>109018428</v>
       </c>
       <c r="B37" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4775,10 +4535,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576920.8608139005</v>
+        <v>576920</v>
       </c>
       <c r="R37" t="n">
-        <v>7050989.22688143</v>
+        <v>7050989</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4847,15 +4607,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109016317</v>
+        <v>109018666</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4893,10 +4648,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576982.8741140434</v>
+        <v>576912</v>
       </c>
       <c r="R38" t="n">
-        <v>7050878.892328644</v>
+        <v>7051104</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4928,7 +4683,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4938,7 +4693,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4953,27 +4708,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109012889</v>
+        <v>109019312</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5000,9 +4750,14 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5011,13 +4766,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577205.2038348324</v>
+        <v>577039</v>
       </c>
       <c r="R39" t="n">
-        <v>7050946.670028023</v>
+        <v>7051116</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5046,7 +4801,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5056,7 +4811,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5083,15 +4838,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109018888</v>
+        <v>109020039</v>
       </c>
       <c r="B40" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5099,35 +4849,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576942.6114046342</v>
+        <v>577004</v>
       </c>
       <c r="R40" t="n">
-        <v>7051159.507415119</v>
+        <v>7051066</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -5159,7 +4914,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5169,7 +4924,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,27 +4939,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109016758</v>
+        <v>109020099</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5233,7 +4983,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5242,10 +4992,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577002.7239883865</v>
+        <v>577018</v>
       </c>
       <c r="R41" t="n">
-        <v>7050888.285096596</v>
+        <v>7051029</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -5277,7 +5027,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5287,7 +5037,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5302,27 +5052,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109018189</v>
+        <v>109242264</v>
       </c>
       <c r="B42" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5330,38 +5075,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576969.8624173822</v>
+        <v>577122</v>
       </c>
       <c r="R42" t="n">
-        <v>7050973.928546304</v>
+        <v>7051003</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5385,22 +5135,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5415,27 +5155,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109018567</v>
+        <v>109242306</v>
       </c>
       <c r="B43" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5443,38 +5178,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576906.898265689</v>
+        <v>577160</v>
       </c>
       <c r="R43" t="n">
-        <v>7051049.929696585</v>
+        <v>7051026</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5498,22 +5238,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,27 +5258,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>109017942</v>
+        <v>110686312</v>
       </c>
       <c r="B44" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,38 +5281,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577013.9920521642</v>
+        <v>577218</v>
       </c>
       <c r="R44" t="n">
-        <v>7050957.176009397</v>
+        <v>7050951</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5611,22 +5339,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5641,66 +5364,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>109013264</v>
+        <v>110686242</v>
       </c>
       <c r="B45" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220250</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577180.7941994793</v>
+        <v>577267</v>
       </c>
       <c r="R45" t="n">
-        <v>7050904.638621862</v>
+        <v>7050884</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5724,22 +5445,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5748,77 +5459,68 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109018666</v>
+        <v>105359091</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576912.2814167491</v>
+        <v>576889</v>
       </c>
       <c r="R46" t="n">
-        <v>7051103.971253037</v>
+        <v>7051115</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5842,22 +5544,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,477 +5573,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>109020039</v>
-      </c>
-      <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Kylbodarna, Ång</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>577003.7660936043</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7051066.089406643</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>109242306</v>
-      </c>
-      <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Kylbodarna, Ång</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>577159.9931511729</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7051026.217753898</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>109242264</v>
-      </c>
-      <c r="B49" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Kylbodarna, Ång</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>577121.3066520585</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7051002.554490864</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>110686242</v>
-      </c>
-      <c r="B50" t="n">
-        <v>95723</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>220250</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Strutbräken</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Matteuccia struthiopteris</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Kylbodarna, Ång</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>577266.9712248652</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7050883.564450492</v>
-      </c>
-      <c r="S50" t="n">
-        <v>25</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106186475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106186581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105359035</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013264</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109016013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018567</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105358131</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105358184</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105358232</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185805</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185882</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2153,6 +2223,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106185957</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013961</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2369,6 +2449,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018189</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105358298</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105359395</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109012695</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2801,6 +2901,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109012889</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013388</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3027,6 +3137,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013589</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109013867</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3253,6 +3373,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109014228</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3366,6 +3491,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109014420</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3474,6 +3604,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109014693</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3587,6 +3722,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109015165</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3700,6 +3840,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109015538</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3813,6 +3958,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109016063</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3926,6 +4076,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109016170</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4039,6 +4194,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109016317</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4152,6 +4312,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109016758</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4265,6 +4430,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109017070</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4378,6 +4548,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109017215</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4491,6 +4666,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018004</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4604,6 +4784,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018428</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4717,6 +4902,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109018666</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4835,6 +5025,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109019312</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4948,6 +5143,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109020039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5061,6 +5261,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109020099</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5164,6 +5369,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109242264</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5267,6 +5477,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109242306</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5373,6 +5588,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110686312</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5475,6 +5695,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110686242</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5573,8 +5798,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105359091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>135597182</v>
       </c>
       <c r="B24" t="n">
-        <v>79912</v>
+        <v>79950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135597217</v>
       </c>
       <c r="B25" t="n">
-        <v>79912</v>
+        <v>79950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135597177</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135597187</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>135597194</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>135597198</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>135597207</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135597213</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135597219</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>135597195</v>
       </c>
       <c r="B44" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>135597204</v>
       </c>
       <c r="B45" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135597212</v>
       </c>
       <c r="B46" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>135597200</v>
       </c>
       <c r="B48" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135597199</v>
       </c>
       <c r="B49" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135597174</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>135597185</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>135597201</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>135597202</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>135597206</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>135597218</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>135597175</v>
       </c>
       <c r="B87" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>92260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>135597182</v>
       </c>
       <c r="B24" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135597217</v>
       </c>
       <c r="B25" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135597177</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135597187</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>135597194</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>135597198</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>135597207</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135597213</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135597219</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>135597195</v>
       </c>
       <c r="B44" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>135597204</v>
       </c>
       <c r="B45" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135597212</v>
       </c>
       <c r="B46" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>135597200</v>
       </c>
       <c r="B48" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135597199</v>
       </c>
       <c r="B49" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>135597175</v>
       </c>
       <c r="B87" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92265</v>
+        <v>92267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92267</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>135597182</v>
       </c>
       <c r="B24" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135597217</v>
       </c>
       <c r="B25" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135597177</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135597187</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>135597194</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>135597198</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>135597207</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135597213</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135597219</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>135597195</v>
       </c>
       <c r="B44" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>135597204</v>
       </c>
       <c r="B45" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135597212</v>
       </c>
       <c r="B46" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>135597200</v>
       </c>
       <c r="B48" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135597199</v>
       </c>
       <c r="B49" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>135597174</v>
       </c>
       <c r="B77" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>135597185</v>
       </c>
       <c r="B78" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>135597201</v>
       </c>
       <c r="B79" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>135597202</v>
       </c>
       <c r="B80" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>135597206</v>
       </c>
       <c r="B81" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>135597218</v>
       </c>
       <c r="B82" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>135597175</v>
       </c>
       <c r="B87" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>135597182</v>
       </c>
       <c r="B24" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>135597217</v>
       </c>
       <c r="B25" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135597177</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>135597187</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>135597194</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>135597198</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>135597207</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135597213</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135597219</v>
       </c>
       <c r="B43" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>135597195</v>
       </c>
       <c r="B44" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>135597204</v>
       </c>
       <c r="B45" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>135597212</v>
       </c>
       <c r="B46" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>135597200</v>
       </c>
       <c r="B48" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>135597199</v>
       </c>
       <c r="B49" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>135597175</v>
       </c>
       <c r="B87" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 59045-2022 artfynd.xlsx
+++ b/artfynd/A 59045-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597209</v>
       </c>
       <c r="B2" t="n">
-        <v>92282</v>
+        <v>92283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135597210</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135597191</v>
       </c>
       <c r="B6" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>135597196</v>
       </c>
       <c r="B7" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135597181</v>
       </c>
       <c r="B8" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>135597190</v>
       </c>
       <c r="B9" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>135597216</v>
       </c>
       <c r="B10" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135597183</v>
       </c>
       <c r="B11" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135597188</v>
       </c>
       <c r="B12" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135597220</v>
       </c>
       <c r="B13" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>135597179</v>
       </c>
       <c r="B19" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135597193</v>
       </c>
       <c r="B20" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>135597214</v>
       </c>
       <c r="B21" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>135597192</v>
       </c>
       <c r="B22" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>135597189</v>
       </c>
       <c r="B26" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135597180</v>
       </c>
       <c r="B27" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>135597205</v>
       </c>
       <c r="B28" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>135597215</v>
       </c>
       <c r="B29" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>135597184</v>
       </c>
       <c r="B84" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135597203</v>
       </c>
       <c r="B85" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135597208</v>
       </c>
       <c r="B86" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>135597178</v>
       </c>
       <c r="B89" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
